--- a/Laliga25-26-transfmkt.xlsx
+++ b/Laliga25-26-transfmkt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AA-DADES\Arxius-Python\Pruebo-streamilt-julio-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80896841-D221-4A62-9ACF-FD5EB288956D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F417846B-D4E4-4862-8DEA-F8447B1DF1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34215" yWindow="2070" windowWidth="21600" windowHeight="12975" firstSheet="24" activeTab="37" xr2:uid="{25762EF5-D697-4512-9C55-A2D3271D8802}"/>
+    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="37" xr2:uid="{25762EF5-D697-4512-9C55-A2D3271D8802}"/>
   </bookViews>
   <sheets>
     <sheet name="J1" sheetId="1" r:id="rId1"/>
@@ -288,7 +288,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="55">
   <si>
     <t>#</t>
   </si>
@@ -451,12 +451,27 @@
   <si>
     <t>58:60</t>
   </si>
+  <si>
+    <t>Table LaLiga</t>
+  </si>
+  <si>
+    <t>59:61</t>
+  </si>
+  <si>
+    <t>46:60</t>
+  </si>
+  <si>
+    <t>47:61</t>
+  </si>
+  <si>
+    <t>26:60</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,6 +519,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -645,7 +666,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
@@ -700,6 +721,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8562,6 +8586,259 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing38.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1" descr="Spanish Cup winner  2025">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7DBFC0D-F38D-FCF1-A54C-028686FFD693}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="373380"/>
+          <a:ext cx="106680" cy="106680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2" descr="Spanish Champion 2025">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F9221FC-B8F6-D2F2-2A55-3E381DD74C1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1699260" y="373380"/>
+          <a:ext cx="106680" cy="106680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3" descr="FIFA Intercontinental Cup Winner 2025">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95998AC7-D384-E7ED-F0AB-369286400B36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="563880"/>
+          <a:ext cx="106680" cy="106680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4" descr="Spanish 2nd tier champion 2025">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7181874-A000-268F-49C6-74DF9D9E79AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="3596640"/>
+          <a:ext cx="106680" cy="106680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -32310,10 +32587,708 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{564233EF-6144-4049-85D6-3B8C3BE8AFCB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="8">
+        <v>38</v>
+      </c>
+      <c r="E3" s="8">
+        <v>31</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8">
+        <v>6</v>
+      </c>
+      <c r="H3" s="16">
+        <v>3.9833333333333334</v>
+      </c>
+      <c r="I3" s="8">
+        <v>59</v>
+      </c>
+      <c r="J3" s="5">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="6" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8">
+        <v>38</v>
+      </c>
+      <c r="E4" s="8">
+        <v>27</v>
+      </c>
+      <c r="F4" s="8">
+        <v>5</v>
+      </c>
+      <c r="G4" s="8">
+        <v>6</v>
+      </c>
+      <c r="H4" s="16">
+        <v>3.2326388888888888</v>
+      </c>
+      <c r="I4" s="8">
+        <v>42</v>
+      </c>
+      <c r="J4" s="5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="6" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="8">
+        <v>38</v>
+      </c>
+      <c r="E5" s="8">
+        <v>22</v>
+      </c>
+      <c r="F5" s="8">
+        <v>6</v>
+      </c>
+      <c r="G5" s="8">
+        <v>10</v>
+      </c>
+      <c r="H5" s="16">
+        <v>3.0319444444444446</v>
+      </c>
+      <c r="I5" s="8">
+        <v>26</v>
+      </c>
+      <c r="J5" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="6" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="8">
+        <v>38</v>
+      </c>
+      <c r="E6" s="8">
+        <v>21</v>
+      </c>
+      <c r="F6" s="8">
+        <v>6</v>
+      </c>
+      <c r="G6" s="8">
+        <v>11</v>
+      </c>
+      <c r="H6" s="16">
+        <v>2.6138888888888889</v>
+      </c>
+      <c r="I6" s="8">
+        <v>18</v>
+      </c>
+      <c r="J6" s="5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="6" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="8">
+        <v>38</v>
+      </c>
+      <c r="E7" s="8">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8">
+        <v>8</v>
+      </c>
+      <c r="H7" s="16">
+        <v>2.4916666666666667</v>
+      </c>
+      <c r="I7" s="8">
+        <v>11</v>
+      </c>
+      <c r="J7" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="6" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="8">
+        <v>38</v>
+      </c>
+      <c r="E8" s="8">
+        <v>14</v>
+      </c>
+      <c r="F8" s="8">
+        <v>12</v>
+      </c>
+      <c r="G8" s="8">
+        <v>12</v>
+      </c>
+      <c r="H8" s="16">
+        <v>2.2416666666666667</v>
+      </c>
+      <c r="I8" s="8">
+        <v>5</v>
+      </c>
+      <c r="J8" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="6" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="8">
+        <v>38</v>
+      </c>
+      <c r="E9" s="8">
+        <v>15</v>
+      </c>
+      <c r="F9" s="8">
+        <v>6</v>
+      </c>
+      <c r="G9" s="8">
+        <v>17</v>
+      </c>
+      <c r="H9" s="16">
+        <v>1.3597222222222223</v>
+      </c>
+      <c r="I9" s="8">
+        <v>-6</v>
+      </c>
+      <c r="J9" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="6" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="8">
+        <v>38</v>
+      </c>
+      <c r="E10" s="8">
+        <v>12</v>
+      </c>
+      <c r="F10" s="8">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8">
+        <v>12</v>
+      </c>
+      <c r="H10" s="16">
+        <v>1.7388888888888889</v>
+      </c>
+      <c r="I10" s="8">
+        <v>-3</v>
+      </c>
+      <c r="J10" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="6" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="8">
+        <v>38</v>
+      </c>
+      <c r="E11" s="8">
+        <v>13</v>
+      </c>
+      <c r="F11" s="8">
+        <v>10</v>
+      </c>
+      <c r="G11" s="8">
+        <v>15</v>
+      </c>
+      <c r="H11" s="16">
+        <v>1.9548611111111112</v>
+      </c>
+      <c r="I11" s="8">
+        <v>-9</v>
+      </c>
+      <c r="J11" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="6" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="8">
+        <v>38</v>
+      </c>
+      <c r="E12" s="8">
+        <v>11</v>
+      </c>
+      <c r="F12" s="8">
+        <v>13</v>
+      </c>
+      <c r="G12" s="8">
+        <v>14</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="8">
+        <v>-2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="8">
+        <v>38</v>
+      </c>
+      <c r="E13" s="8">
+        <v>12</v>
+      </c>
+      <c r="F13" s="8">
+        <v>10</v>
+      </c>
+      <c r="G13" s="8">
+        <v>16</v>
+      </c>
+      <c r="H13" s="16">
+        <v>1.8298611111111112</v>
+      </c>
+      <c r="I13" s="8">
+        <v>-12</v>
+      </c>
+      <c r="J13" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="6" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="8">
+        <v>38</v>
+      </c>
+      <c r="E14" s="8">
+        <v>13</v>
+      </c>
+      <c r="F14" s="8">
+        <v>6</v>
+      </c>
+      <c r="G14" s="8">
+        <v>19</v>
+      </c>
+      <c r="H14" s="16">
+        <v>1.8319444444444444</v>
+      </c>
+      <c r="I14" s="8">
+        <v>-15</v>
+      </c>
+      <c r="J14" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="6" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="8">
+        <v>38</v>
+      </c>
+      <c r="E15" s="8">
+        <v>12</v>
+      </c>
+      <c r="F15" s="8">
+        <v>7</v>
+      </c>
+      <c r="G15" s="8">
+        <v>19</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="8">
+        <v>-14</v>
+      </c>
+      <c r="J15" s="5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="6" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="8">
+        <v>38</v>
+      </c>
+      <c r="E16" s="8">
+        <v>11</v>
+      </c>
+      <c r="F16" s="8">
+        <v>10</v>
+      </c>
+      <c r="G16" s="8">
+        <v>17</v>
+      </c>
+      <c r="H16" s="16">
+        <v>1.8722222222222222</v>
+      </c>
+      <c r="I16" s="8">
+        <v>-12</v>
+      </c>
+      <c r="J16" s="5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="6" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="8">
+        <v>38</v>
+      </c>
+      <c r="E17" s="8">
+        <v>10</v>
+      </c>
+      <c r="F17" s="8">
+        <v>13</v>
+      </c>
+      <c r="G17" s="8">
+        <v>15</v>
+      </c>
+      <c r="H17" s="16">
+        <v>2.0812499999999998</v>
+      </c>
+      <c r="I17" s="8">
+        <v>-8</v>
+      </c>
+      <c r="J17" s="5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="6" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="8">
+        <v>38</v>
+      </c>
+      <c r="E18" s="8">
+        <v>11</v>
+      </c>
+      <c r="F18" s="8">
+        <v>9</v>
+      </c>
+      <c r="G18" s="8">
+        <v>18</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="8">
+        <v>-14</v>
+      </c>
+      <c r="J18" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="6" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="8">
+        <v>38</v>
+      </c>
+      <c r="E19" s="8">
+        <v>11</v>
+      </c>
+      <c r="F19" s="8">
+        <v>9</v>
+      </c>
+      <c r="G19" s="8">
+        <v>18</v>
+      </c>
+      <c r="H19" s="16">
+        <v>1.8680555555555556</v>
+      </c>
+      <c r="I19" s="8">
+        <v>-6</v>
+      </c>
+      <c r="J19" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="6" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="8">
+        <v>38</v>
+      </c>
+      <c r="E20" s="8">
+        <v>11</v>
+      </c>
+      <c r="F20" s="8">
+        <v>9</v>
+      </c>
+      <c r="G20" s="8">
+        <v>18</v>
+      </c>
+      <c r="H20" s="16">
+        <v>1.9979166666666666</v>
+      </c>
+      <c r="I20" s="8">
+        <v>-10</v>
+      </c>
+      <c r="J20" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="6" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="8">
+        <v>38</v>
+      </c>
+      <c r="E21" s="8">
+        <v>9</v>
+      </c>
+      <c r="F21" s="8">
+        <v>14</v>
+      </c>
+      <c r="G21" s="8">
+        <v>15</v>
+      </c>
+      <c r="H21" s="16">
+        <v>1.6631944444444444</v>
+      </c>
+      <c r="I21" s="8">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="6" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="8">
+        <v>38</v>
+      </c>
+      <c r="E22" s="8">
+        <v>6</v>
+      </c>
+      <c r="F22" s="8">
+        <v>11</v>
+      </c>
+      <c r="G22" s="8">
+        <v>21</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" s="8">
+        <v>-34</v>
+      </c>
+      <c r="J22" s="5">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" tooltip="Villarreal CF" display="https://www.transfermarkt.com/fc-villarreal/spielplan/verein/1050/saison_id/2025" xr:uid="{F404DDFA-58C2-4EAD-840A-B52F0D02519F}"/>
+    <hyperlink ref="C6" r:id="rId2" tooltip="Atlético de Madrid" display="https://www.transfermarkt.com/atletico-madrid/spielplan/verein/13/saison_id/2025" xr:uid="{A08A918D-0263-46D1-874D-5C24B919F952}"/>
+    <hyperlink ref="C7" r:id="rId3" tooltip="Real Betis Balompié" display="https://www.transfermarkt.com/real-betis-sevilla/spielplan/verein/150/saison_id/2025" xr:uid="{C81BEE50-D596-4C53-A372-2A5E1D7BD340}"/>
+    <hyperlink ref="C8" r:id="rId4" tooltip="Celta de Vigo" display="https://www.transfermarkt.com/celta-vigo/spielplan/verein/940/saison_id/2025" xr:uid="{D1E7EFB6-1F92-42B4-9172-D6ACECA01ADB}"/>
+    <hyperlink ref="C9" r:id="rId5" tooltip="Getafe CF" display="https://www.transfermarkt.com/fc-getafe/spielplan/verein/3709/saison_id/2025" xr:uid="{34D01CCF-E8D2-4F5F-9E28-61C64474C97E}"/>
+    <hyperlink ref="C10" r:id="rId6" tooltip="Rayo Vallecano" display="https://www.transfermarkt.com/rayo-vallecano/spielplan/verein/367/saison_id/2025" xr:uid="{BE846F9F-5F84-4003-9777-41FE7478F816}"/>
+    <hyperlink ref="C11" r:id="rId7" tooltip="Valencia CF" display="https://www.transfermarkt.com/fc-valencia/spielplan/verein/1049/saison_id/2025" xr:uid="{9F12A394-A203-43D1-BEF1-C89853405C04}"/>
+    <hyperlink ref="C12" r:id="rId8" tooltip="Real Sociedad" display="https://www.transfermarkt.com/real-sociedad-san-sebastian/spielplan/verein/681/saison_id/2025" xr:uid="{200DC1AB-C8B1-4591-B523-1B999034FF8F}"/>
+    <hyperlink ref="C13" r:id="rId9" tooltip="RCD Espanyol Barcelona" display="https://www.transfermarkt.com/espanyol-barcelona/spielplan/verein/714/saison_id/2025" xr:uid="{6CE7F91D-AA85-4C26-B4A4-4B500542CD8D}"/>
+    <hyperlink ref="C14" r:id="rId10" tooltip="Athletic Bilbao" display="https://www.transfermarkt.com/athletic-bilbao/spielplan/verein/621/saison_id/2025" xr:uid="{850CF750-6DF4-404E-B403-B6CCC5638ADF}"/>
+    <hyperlink ref="C15" r:id="rId11" tooltip="Sevilla FC" display="https://www.transfermarkt.com/fc-sevilla/spielplan/verein/368/saison_id/2025" xr:uid="{468EA89E-1A8F-4100-887A-B5D3FA0DE929}"/>
+    <hyperlink ref="C16" r:id="rId12" tooltip="Deportivo Alavés" display="https://www.transfermarkt.com/deportivo-alaves/spielplan/verein/1108/saison_id/2025" xr:uid="{BE7F86B1-A7E9-41A3-BFBB-834ADA9F5F09}"/>
+    <hyperlink ref="C17" r:id="rId13" tooltip="Elche CF" display="https://www.transfermarkt.com/fc-elche/spielplan/verein/1531/saison_id/2025" xr:uid="{E6D83810-8380-4472-95F3-63DD1E606DE1}"/>
+    <hyperlink ref="C19" r:id="rId14" tooltip="CA Osasuna" display="https://www.transfermarkt.com/ca-osasuna/spielplan/verein/331/saison_id/2025" xr:uid="{2435802B-AA8B-483E-8474-8C4FCDD97D7E}"/>
+    <hyperlink ref="C20" r:id="rId15" tooltip="RCD Mallorca" display="https://www.transfermarkt.com/rcd-mallorca/spielplan/verein/237/saison_id/2025" xr:uid="{A8F8EAD8-E2EF-4715-90A9-39683FDD5C02}"/>
+    <hyperlink ref="C21" r:id="rId16" tooltip="Girona FC" display="https://www.transfermarkt.com/fc-girona/spielplan/verein/12321/saison_id/2025" xr:uid="{929CD5ED-EA4F-4EFD-A81C-26D41F3FA31B}"/>
+    <hyperlink ref="C22" r:id="rId17" tooltip="Real Oviedo" display="https://www.transfermarkt.com/real-oviedo/spielplan/verein/2497/saison_id/2025" xr:uid="{C87CB4E8-8CD7-4261-AA98-D3567310664F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
+  <drawing r:id="rId19"/>
 </worksheet>
 </file>
 
